--- a/artfynd/A 57461-2024 artfynd.xlsx
+++ b/artfynd/A 57461-2024 artfynd.xlsx
@@ -2213,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122197537</v>
+        <v>122197331</v>
       </c>
       <c r="B16" t="n">
-        <v>79686</v>
+        <v>79661</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2229,21 +2229,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>6457</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463290</v>
+        <v>463296</v>
       </c>
       <c r="R16" t="n">
-        <v>7025849</v>
+        <v>7025833</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På asp (45 cm dbh) i sumpskog</t>
+          <t>På asp i kanten av sumpskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122198176</v>
+        <v>122199884</v>
       </c>
       <c r="B17" t="n">
-        <v>98175</v>
+        <v>91219</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,48 +2346,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463283</v>
+        <v>463326</v>
       </c>
       <c r="R17" t="n">
-        <v>7025932</v>
+        <v>7025889</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,7 +2405,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2429,12 +2415,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Plus 1 vinterståndare</t>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2461,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122199884</v>
+        <v>122199987</v>
       </c>
       <c r="B18" t="n">
-        <v>91219</v>
+        <v>79630</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2473,25 +2459,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2536,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2546,12 +2532,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På rönn i kanten av lok</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2578,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122198393</v>
+        <v>122200098</v>
       </c>
       <c r="B19" t="n">
-        <v>90779</v>
+        <v>79630</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2590,46 +2576,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463306</v>
+        <v>463325</v>
       </c>
       <c r="R19" t="n">
-        <v>7025975</v>
+        <v>7025856</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2658,7 +2639,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2649,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På 5 grova aspar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122198645</v>
+        <v>122197601</v>
       </c>
       <c r="B20" t="n">
-        <v>98175</v>
+        <v>90797</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,50 +2693,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463345</v>
+        <v>463290</v>
       </c>
       <c r="R20" t="n">
-        <v>7025953</v>
+        <v>7025849</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2779,7 +2756,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2789,12 +2766,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>På granhögstubbe (60 cm dbh) i gammal granskog vid sumpskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2809,22 +2786,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122199987</v>
+        <v>122197537</v>
       </c>
       <c r="B21" t="n">
-        <v>79630</v>
+        <v>79686</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2837,21 +2814,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2861,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463326</v>
+        <v>463290</v>
       </c>
       <c r="R21" t="n">
-        <v>7025889</v>
+        <v>7025849</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2896,7 +2873,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2906,12 +2883,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På rönn i kanten av lok</t>
+          <t>På asp (45 cm dbh) i sumpskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2938,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122197008</v>
+        <v>122198000</v>
       </c>
       <c r="B22" t="n">
-        <v>79755</v>
+        <v>79761</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2954,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2978,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463286</v>
+        <v>463260</v>
       </c>
       <c r="R22" t="n">
-        <v>7025849</v>
+        <v>7025887</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3013,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3023,12 +3000,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På asp i sumpskog</t>
+          <t>På bark på stam av levande gammal asp (60 cm dbh)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,17 +3025,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122198000</v>
+        <v>122197684</v>
       </c>
       <c r="B23" t="n">
-        <v>79761</v>
+        <v>79692</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3071,37 +3048,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>229748</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463260</v>
+        <v>463272</v>
       </c>
       <c r="R23" t="n">
-        <v>7025887</v>
+        <v>7025866</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3130,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3140,12 +3122,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (60 cm dbh)</t>
+          <t>På gammal sälj, ca 55cm i diameter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3160,19 +3142,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122198408</v>
+        <v>122198688</v>
       </c>
       <c r="B24" t="n">
         <v>98175</v>
@@ -3207,7 +3189,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3215,24 +3197,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463298</v>
+        <v>463359</v>
       </c>
       <c r="R24" t="n">
-        <v>7025964</v>
+        <v>7025954</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3261,7 +3238,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,12 +3248,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>I gammal barrblandskog</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3291,22 +3263,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122200106</v>
+        <v>122197434</v>
       </c>
       <c r="B25" t="n">
-        <v>79686</v>
+        <v>79762</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3319,21 +3291,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3343,10 +3315,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463316</v>
+        <v>463279</v>
       </c>
       <c r="R25" t="n">
-        <v>7025877</v>
+        <v>7025856</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3378,7 +3350,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,12 +3360,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På grov asp vid fuktsänka</t>
+          <t>På bark på stam av levande asp 37 cm dbh i sumpskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3420,10 +3392,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122197086</v>
+        <v>122198645</v>
       </c>
       <c r="B26" t="n">
-        <v>79761</v>
+        <v>98175</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3432,41 +3404,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>463286</v>
+        <v>463345</v>
       </c>
       <c r="R26" t="n">
-        <v>7025849</v>
+        <v>7025953</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3495,7 +3476,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3505,12 +3486,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På asp i sumpskog</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3525,22 +3506,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122197434</v>
+        <v>122200307</v>
       </c>
       <c r="B27" t="n">
-        <v>79762</v>
+        <v>91219</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3549,25 +3530,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3577,10 +3558,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463279</v>
+        <v>463324</v>
       </c>
       <c r="R27" t="n">
-        <v>7025856</v>
+        <v>7025865</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3612,7 +3593,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3622,12 +3603,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp 37 cm dbh i sumpskog</t>
+          <t>På granlåga i område med rikligt med lågor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3654,10 +3635,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122197113</v>
+        <v>122197705</v>
       </c>
       <c r="B28" t="n">
-        <v>79686</v>
+        <v>79755</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3670,21 +3651,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3675,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463286</v>
+        <v>463269</v>
       </c>
       <c r="R28" t="n">
-        <v>7025849</v>
+        <v>7025876</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3729,7 +3710,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3739,12 +3720,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På asp i sumpskog</t>
+          <t>På gammal asp vid lok</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3764,14 +3745,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122198688</v>
+        <v>122198408</v>
       </c>
       <c r="B29" t="n">
         <v>98175</v>
@@ -3806,7 +3787,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3814,19 +3795,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463359</v>
+        <v>463298</v>
       </c>
       <c r="R29" t="n">
-        <v>7025954</v>
+        <v>7025964</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3855,7 +3841,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3865,7 +3851,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3880,22 +3871,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122197601</v>
+        <v>122197944</v>
       </c>
       <c r="B30" t="n">
-        <v>90797</v>
+        <v>74747</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3908,21 +3899,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3932,10 +3923,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463290</v>
+        <v>463262</v>
       </c>
       <c r="R30" t="n">
-        <v>7025849</v>
+        <v>7025915</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3967,7 +3958,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3977,12 +3968,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granhögstubbe (60 cm dbh) i gammal granskog vid sumpskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3997,22 +3988,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122197944</v>
+        <v>122197008</v>
       </c>
       <c r="B31" t="n">
-        <v>74747</v>
+        <v>79755</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4021,25 +4012,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4049,10 +4040,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463262</v>
+        <v>463286</v>
       </c>
       <c r="R31" t="n">
-        <v>7025915</v>
+        <v>7025849</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4084,7 +4075,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4094,12 +4085,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På asp i sumpskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4114,22 +4105,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122197331</v>
+        <v>122196898</v>
       </c>
       <c r="B32" t="n">
-        <v>79661</v>
+        <v>74747</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4138,25 +4129,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6457</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4166,10 +4157,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463296</v>
+        <v>463285</v>
       </c>
       <c r="R32" t="n">
-        <v>7025833</v>
+        <v>7025820</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4201,7 +4192,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4211,12 +4202,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På asp i kanten av sumpskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4231,12 +4222,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4360,10 +4351,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122198696</v>
+        <v>122197086</v>
       </c>
       <c r="B34" t="n">
-        <v>98175</v>
+        <v>79761</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4372,52 +4363,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463352</v>
+        <v>463286</v>
       </c>
       <c r="R34" t="n">
-        <v>7025942</v>
+        <v>7025849</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4449,7 +4426,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4459,12 +4436,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>På asp i sumpskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4484,17 +4461,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122200098</v>
+        <v>122198696</v>
       </c>
       <c r="B35" t="n">
-        <v>79630</v>
+        <v>98175</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4503,41 +4480,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463325</v>
+        <v>463352</v>
       </c>
       <c r="R35" t="n">
-        <v>7025856</v>
+        <v>7025942</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4566,7 +4557,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4576,12 +4567,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På 5 grova aspar</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4596,22 +4587,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122199784</v>
+        <v>122198393</v>
       </c>
       <c r="B36" t="n">
-        <v>90797</v>
+        <v>90779</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4624,37 +4615,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463373</v>
+        <v>463306</v>
       </c>
       <c r="R36" t="n">
-        <v>7025896</v>
+        <v>7025975</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4683,7 +4679,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4693,12 +4689,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På granhögstubbe</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4713,19 +4704,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122196898</v>
+        <v>122197822</v>
       </c>
       <c r="B37" t="n">
         <v>74747</v>
@@ -4765,10 +4756,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463285</v>
+        <v>463288</v>
       </c>
       <c r="R37" t="n">
-        <v>7025820</v>
+        <v>7025914</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4800,7 +4791,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4810,12 +4801,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4830,22 +4821,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122200307</v>
+        <v>122199784</v>
       </c>
       <c r="B38" t="n">
-        <v>91219</v>
+        <v>90797</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4854,25 +4845,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4882,10 +4873,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463324</v>
+        <v>463373</v>
       </c>
       <c r="R38" t="n">
-        <v>7025865</v>
+        <v>7025896</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4917,7 +4908,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4927,12 +4918,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På granlåga i område med rikligt med lågor</t>
+          <t>På granhögstubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4959,10 +4950,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122197705</v>
+        <v>122197113</v>
       </c>
       <c r="B39" t="n">
-        <v>79755</v>
+        <v>79686</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4975,21 +4966,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4999,10 +4990,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463269</v>
+        <v>463286</v>
       </c>
       <c r="R39" t="n">
-        <v>7025876</v>
+        <v>7025849</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5034,7 +5025,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5044,12 +5035,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal asp vid lok</t>
+          <t>På asp i sumpskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5069,17 +5060,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122197822</v>
+        <v>122200106</v>
       </c>
       <c r="B40" t="n">
-        <v>74747</v>
+        <v>79686</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5088,25 +5079,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5116,10 +5107,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463288</v>
+        <v>463316</v>
       </c>
       <c r="R40" t="n">
-        <v>7025914</v>
+        <v>7025877</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5151,7 +5142,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5161,12 +5152,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På grov asp vid fuktsänka</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5193,10 +5184,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122197684</v>
+        <v>122198176</v>
       </c>
       <c r="B41" t="n">
-        <v>79692</v>
+        <v>98175</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5205,31 +5196,40 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5238,13 +5238,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>463272</v>
+        <v>463283</v>
       </c>
       <c r="R41" t="n">
-        <v>7025866</v>
+        <v>7025932</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal sälj, ca 55cm i diameter</t>
+          <t>Plus 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5303,12 +5303,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 57461-2024 artfynd.xlsx
+++ b/artfynd/A 57461-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107044958</v>
+        <v>122198393</v>
       </c>
       <c r="B2" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229748</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lugnvik, Jmt</t>
+          <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463282.0808308987</v>
+        <v>463306</v>
       </c>
       <c r="R2" t="n">
-        <v>7025872.865324624</v>
+        <v>7025975</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,27 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107044932</v>
+        <v>122199884</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,38 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lugnvik, Jmt</t>
+          <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463282.0808308987</v>
+        <v>463326</v>
       </c>
       <c r="R3" t="n">
-        <v>7025872.865324624</v>
+        <v>7025889</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På granlåga i äldre granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,27 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107044447</v>
+        <v>122200307</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,38 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnvik, Jmt</t>
+          <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463280.9479618013</v>
+        <v>463324</v>
       </c>
       <c r="R4" t="n">
-        <v>7025813.181850063</v>
+        <v>7025865</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På granlåga i område med rikligt med lågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,27 +999,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107044763</v>
+        <v>111705395</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463314.3085940651</v>
+        <v>463189</v>
       </c>
       <c r="R5" t="n">
-        <v>7025861.275408302</v>
+        <v>7025804</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,22 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107044851</v>
+        <v>111708662</v>
       </c>
       <c r="B6" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>3739</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463296.0633070917</v>
+        <v>463337</v>
       </c>
       <c r="R6" t="n">
-        <v>7025877.193656636</v>
+        <v>7025779</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,22 +1175,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107044960</v>
+        <v>111705440</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1218,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463282.0808308987</v>
+        <v>463216</v>
       </c>
       <c r="R7" t="n">
-        <v>7025872.865324624</v>
+        <v>7025821</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,22 +1273,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,54 +1305,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107044590</v>
+        <v>122198465</v>
       </c>
       <c r="B8" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lugnvik, Jmt</t>
+          <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463278.9859107099</v>
+        <v>463345</v>
       </c>
       <c r="R8" t="n">
-        <v>7025798.841097175</v>
+        <v>7025992</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,22 +1375,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,27 +1405,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107044349</v>
+        <v>111708507</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463280.9479618013</v>
+        <v>463315</v>
       </c>
       <c r="R9" t="n">
-        <v>7025813.181850063</v>
+        <v>7025767</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1537,22 +1483,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,37 +1515,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111707460</v>
+        <v>107044447</v>
       </c>
       <c r="B10" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463271</v>
+        <v>463281</v>
       </c>
       <c r="R10" t="n">
-        <v>7025779</v>
+        <v>7025813</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1650,12 +1581,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,56 +1613,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111705879</v>
+        <v>122199479</v>
       </c>
       <c r="B11" t="n">
-        <v>85979</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>249278</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lugnvik, Jmt</t>
+          <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463241</v>
+        <v>463415</v>
       </c>
       <c r="R11" t="n">
-        <v>7025817</v>
+        <v>7025901</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,53 +1678,57 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ej mikrad. Skulle kunna vara lövviolspindling också. Finns en del björk/asp på lokalen, även om kalkgranskog dominerar.</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111708662</v>
+        <v>107044349</v>
       </c>
       <c r="B12" t="n">
-        <v>85313</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3739</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463336</v>
+        <v>463281</v>
       </c>
       <c r="R12" t="n">
-        <v>7025780</v>
+        <v>7025813</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1864,12 +1791,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1896,37 +1823,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111705440</v>
+        <v>107044590</v>
       </c>
       <c r="B13" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463216</v>
+        <v>463279</v>
       </c>
       <c r="R13" t="n">
-        <v>7025821</v>
+        <v>7025799</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1967,12 +1889,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1999,37 +1921,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111708507</v>
+        <v>107044851</v>
       </c>
       <c r="B14" t="n">
-        <v>90687</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2040,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463315</v>
+        <v>463296</v>
       </c>
       <c r="R14" t="n">
-        <v>7025767</v>
+        <v>7025877</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2070,12 +1987,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2102,15 +2019,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111706241</v>
+        <v>122196898</v>
       </c>
       <c r="B15" t="n">
-        <v>85979</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2118,40 +2030,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>249278</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lugnvik, Jmt</t>
+          <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463256</v>
+        <v>463285</v>
       </c>
       <c r="R15" t="n">
-        <v>7025814</v>
+        <v>7025820</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2175,75 +2084,79 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-26</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ej mikrad. Skulle kunna vara lövviolspindling också. Finns en del björk/asp på lokalen, även om kalkgranskog dominerar.</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122197086</v>
+        <v>122197822</v>
       </c>
       <c r="B16" t="n">
-        <v>79772</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2253,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463286</v>
+        <v>463288</v>
       </c>
       <c r="R16" t="n">
-        <v>7025849</v>
+        <v>7025914</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,7 +2201,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2298,12 +2211,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På asp i sumpskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2323,22 +2236,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122199784</v>
+        <v>122197944</v>
       </c>
       <c r="B17" t="n">
-        <v>90857</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2346,21 +2254,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,10 +2278,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463373</v>
+        <v>463262</v>
       </c>
       <c r="R17" t="n">
-        <v>7025896</v>
+        <v>7025915</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,7 +2313,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2415,12 +2323,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granhögstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,49 +2343,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122198000</v>
+        <v>122198437</v>
       </c>
       <c r="B18" t="n">
-        <v>79772</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2487,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463260</v>
+        <v>463327</v>
       </c>
       <c r="R18" t="n">
-        <v>7025887</v>
+        <v>7025985</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,7 +2425,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,12 +2435,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp (60 cm dbh)</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog vid sjö</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,37 +2467,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122197434</v>
+        <v>122199677</v>
       </c>
       <c r="B19" t="n">
-        <v>79773</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2502,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463279</v>
+        <v>463417</v>
       </c>
       <c r="R19" t="n">
-        <v>7025856</v>
+        <v>7025881</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,7 +2537,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2649,12 +2547,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp 37 cm dbh i sumpskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,15 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122197113</v>
+        <v>122197146</v>
       </c>
       <c r="B20" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,21 +2590,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2721,10 +2614,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463286</v>
+        <v>463291</v>
       </c>
       <c r="R20" t="n">
-        <v>7025849</v>
+        <v>7025843</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2756,7 +2649,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2766,7 +2659,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2791,44 +2684,39 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122197822</v>
+        <v>122198832</v>
       </c>
       <c r="B21" t="n">
-        <v>74757</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,10 +2726,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463288</v>
+        <v>463367</v>
       </c>
       <c r="R21" t="n">
-        <v>7025914</v>
+        <v>7025952</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2873,7 +2761,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2883,12 +2771,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,37 +2803,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122196898</v>
+        <v>122199987</v>
       </c>
       <c r="B22" t="n">
-        <v>74757</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2838,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463285</v>
+        <v>463326</v>
       </c>
       <c r="R22" t="n">
-        <v>7025820</v>
+        <v>7025889</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,7 +2873,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,12 +2883,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På rönn i kanten av lok</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3020,74 +2903,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122198688</v>
+        <v>122200098</v>
       </c>
       <c r="B23" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463359</v>
+        <v>463325</v>
       </c>
       <c r="R23" t="n">
-        <v>7025954</v>
+        <v>7025856</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3116,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3126,7 +2995,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På 5 grova aspar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,37 +3027,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122197601</v>
+        <v>122197331</v>
       </c>
       <c r="B24" t="n">
-        <v>90857</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6457</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +3062,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463290</v>
+        <v>463296</v>
       </c>
       <c r="R24" t="n">
-        <v>7025849</v>
+        <v>7025833</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,7 +3097,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,12 +3107,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granhögstubbe (60 cm dbh) i gammal granskog vid sumpskog</t>
+          <t>På asp i kanten av sumpskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3263,65 +3132,55 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122198393</v>
+        <v>122197008</v>
       </c>
       <c r="B25" t="n">
-        <v>90839</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>463306</v>
+        <v>463286</v>
       </c>
       <c r="R25" t="n">
-        <v>7025975</v>
+        <v>7025849</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3350,7 +3209,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3360,7 +3219,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På asp i sumpskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3375,27 +3239,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122197537</v>
+        <v>122197705</v>
       </c>
       <c r="B26" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3403,21 +3262,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3427,10 +3286,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>463290</v>
+        <v>463269</v>
       </c>
       <c r="R26" t="n">
-        <v>7025849</v>
+        <v>7025876</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3462,7 +3321,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3472,12 +3331,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På asp (45 cm dbh) i sumpskog</t>
+          <t>På gammal asp vid lok</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3504,67 +3363,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122198408</v>
+        <v>107044763</v>
       </c>
       <c r="B27" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lugnvik, Lugnvik, Jmt</t>
+          <t>Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463298</v>
+        <v>463314</v>
       </c>
       <c r="R27" t="n">
-        <v>7025964</v>
+        <v>7025862</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3588,27 +3429,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>I gammal barrblandskog</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3623,76 +3449,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122198696</v>
+        <v>122197086</v>
       </c>
       <c r="B28" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>463352</v>
+        <v>463286</v>
       </c>
       <c r="R28" t="n">
-        <v>7025942</v>
+        <v>7025849</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3724,7 +3531,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3734,12 +3541,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>På asp i sumpskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3759,44 +3566,39 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122199884</v>
+        <v>122198000</v>
       </c>
       <c r="B29" t="n">
-        <v>91277</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3806,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463326</v>
+        <v>463260</v>
       </c>
       <c r="R29" t="n">
-        <v>7025889</v>
+        <v>7025887</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3841,7 +3643,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3851,12 +3653,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På granlåga i äldre granskog</t>
+          <t>På bark på stam av levande gammal asp (60 cm dbh)</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3883,15 +3685,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122197146</v>
+        <v>122197434</v>
       </c>
       <c r="B30" t="n">
-        <v>79641</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3899,21 +3696,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3923,10 +3720,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>463291</v>
+        <v>463279</v>
       </c>
       <c r="R30" t="n">
-        <v>7025843</v>
+        <v>7025856</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,7 +3755,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3968,12 +3765,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På asp i sumpskog</t>
+          <t>På bark på stam av levande asp 37 cm dbh i sumpskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4000,15 +3797,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122197331</v>
+        <v>122198817</v>
       </c>
       <c r="B31" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4016,37 +3808,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6457</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463296</v>
+        <v>463237</v>
       </c>
       <c r="R31" t="n">
-        <v>7025833</v>
+        <v>7025936</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4075,7 +3876,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4085,12 +3886,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På asp i kanten av sumpskog</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4105,74 +3901,68 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122198645</v>
+        <v>108593844</v>
       </c>
       <c r="B32" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100077</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lugnvik, Lugnvik, Jmt</t>
+          <t>Nälden NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463345</v>
+        <v>463340</v>
       </c>
       <c r="R32" t="n">
-        <v>7025953</v>
+        <v>7025984</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4196,27 +3986,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:57</t>
+          <t>2023-04-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:57</t>
+          <t>2023-04-30</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog</t>
+          <t>Några dagar gamla spår på isen utmed strandkanten.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4231,65 +4011,64 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122197705</v>
+        <v>104916375</v>
       </c>
       <c r="B33" t="n">
-        <v>79766</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lugnvik, Lugnvik, Jmt</t>
+          <t>Nälden NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463269</v>
+        <v>463378</v>
       </c>
       <c r="R33" t="n">
-        <v>7025876</v>
+        <v>7025885</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4313,27 +4092,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2022-12-04</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal asp vid lok</t>
+          <t>Flertal bladrosetter.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4342,68 +4111,78 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122197008</v>
+        <v>122198176</v>
       </c>
       <c r="B34" t="n">
-        <v>79766</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463286</v>
+        <v>463283</v>
       </c>
       <c r="R34" t="n">
-        <v>7025849</v>
+        <v>7025932</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4435,7 +4214,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4445,12 +4224,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På asp i sumpskog</t>
+          <t>Plus 1 vinterståndare</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,57 +4249,66 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122199987</v>
+        <v>122198408</v>
       </c>
       <c r="B35" t="n">
-        <v>79641</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463326</v>
+        <v>463298</v>
       </c>
       <c r="R35" t="n">
-        <v>7025889</v>
+        <v>7025964</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4552,7 +4340,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4562,12 +4350,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På rönn i kanten av lok</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4594,53 +4382,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122197944</v>
+        <v>122198645</v>
       </c>
       <c r="B36" t="n">
-        <v>74757</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>463262</v>
+        <v>463345</v>
       </c>
       <c r="R36" t="n">
-        <v>7025915</v>
+        <v>7025953</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4669,7 +4461,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4679,12 +4471,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4711,15 +4503,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122198176</v>
+        <v>122198688</v>
       </c>
       <c r="B37" t="n">
-        <v>98237</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4533,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4754,24 +4541,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>463283</v>
+        <v>463359</v>
       </c>
       <c r="R37" t="n">
-        <v>7025932</v>
+        <v>7025954</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4800,7 +4582,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4810,12 +4592,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Plus 1 vinterståndare</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4830,55 +4607,59 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122197684</v>
+        <v>122198696</v>
       </c>
       <c r="B38" t="n">
-        <v>79703</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4887,13 +4668,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>463272</v>
+        <v>463352</v>
       </c>
       <c r="R38" t="n">
-        <v>7025866</v>
+        <v>7025942</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4922,7 +4703,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4932,12 +4713,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal sälj, ca 55cm i diameter</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4952,65 +4733,61 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122200307</v>
+        <v>107044960</v>
       </c>
       <c r="B39" t="n">
-        <v>91277</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>229497</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lugnvik, Lugnvik, Jmt</t>
+          <t>Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>463324</v>
+        <v>463282</v>
       </c>
       <c r="R39" t="n">
-        <v>7025865</v>
+        <v>7025873</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5034,27 +4811,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På granlåga i område med rikligt med lågor</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5069,27 +4831,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122200098</v>
+        <v>122197113</v>
       </c>
       <c r="B40" t="n">
-        <v>79641</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5097,21 +4854,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5121,13 +4878,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>463325</v>
+        <v>463286</v>
       </c>
       <c r="R40" t="n">
-        <v>7025856</v>
+        <v>7025849</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5156,7 +4913,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5166,12 +4923,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På 5 grova aspar</t>
+          <t>På asp i sumpskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5186,27 +4943,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122200106</v>
+        <v>122197537</v>
       </c>
       <c r="B41" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,10 +4990,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>463316</v>
+        <v>463290</v>
       </c>
       <c r="R41" t="n">
-        <v>7025877</v>
+        <v>7025849</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5273,7 +5025,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5283,12 +5035,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På grov asp vid fuktsänka</t>
+          <t>På asp (45 cm dbh) i sumpskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5315,57 +5067,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>104916375</v>
+        <v>122200106</v>
       </c>
       <c r="B42" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Nälden NÖ, Jmt</t>
+          <t>Lugnvik, Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>463377.9547934636</v>
+        <v>463316</v>
       </c>
       <c r="R42" t="n">
-        <v>7025885.234146616</v>
+        <v>7025877</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5389,27 +5132,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Flertal bladrosetter.</t>
+          <t>På grov asp vid fuktsänka</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5418,72 +5161,67 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122199677</v>
+        <v>107044958</v>
       </c>
       <c r="B43" t="n">
-        <v>74757</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80398</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>229748</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lugnvik, Lugnvik, Jmt</t>
+          <t>Lugnvik, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>463417</v>
+        <v>463282</v>
       </c>
       <c r="R43" t="n">
-        <v>7025881</v>
+        <v>7025873</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5507,27 +5245,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5542,15 +5265,470 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122197684</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lugnvik, Lugnvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>463272</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7025866</v>
+      </c>
+      <c r="S44" t="n">
+        <v>8</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gammal sälj, ca 55cm i diameter</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>111705879</v>
+      </c>
+      <c r="B45" t="n">
+        <v>87099</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lugnvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>463241</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7025817</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ej mikrad. Skulle kunna vara lövviolspindling också. Finns en del björk/asp på lokalen, även om kalkgranskog dominerar.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>111706241</v>
+      </c>
+      <c r="B46" t="n">
+        <v>87099</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>249278</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Barrviolspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius harcynicus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Pers.) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lugnvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>463256</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7025814</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-08-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ej mikrad. Skulle kunna vara lövviolspindling också. Finns en del björk/asp på lokalen, även om kalkgranskog dominerar.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>122198436</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lugnvik, Lugnvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>463313</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7025981</v>
+      </c>
+      <c r="S47" t="n">
+        <v>9</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Näskott</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Längst ut på en gren</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57461-2024 artfynd.xlsx
+++ b/artfynd/A 57461-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122198393</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122199884</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122200307</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111705395</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111708662</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111705440</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122198465</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111708507</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107044447</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122199479</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1820,6 +1875,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107044349</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107044590</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2016,6 +2081,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107044851</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2128,6 +2198,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122196898</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2240,6 +2315,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122197822</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2352,6 +2432,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122197944</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2464,6 +2549,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122198437</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2576,6 +2666,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122199677</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2688,6 +2783,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122197146</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2800,6 +2900,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122198832</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2912,6 +3017,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122199987</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3024,6 +3134,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122200098</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3136,6 +3251,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122197331</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3248,6 +3368,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122197008</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3360,6 +3485,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122197705</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3458,6 +3588,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107044763</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3570,6 +3705,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122197086</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3682,6 +3822,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122198000</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3794,6 +3939,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122197434</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3910,6 +4060,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122198817</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4020,6 +4175,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108593844</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4127,6 +4287,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104916375</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4253,6 +4418,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122198176</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4379,6 +4549,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122198408</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4500,6 +4675,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122198645</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4616,6 +4796,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122198688</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4742,6 +4927,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122198696</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4840,6 +5030,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107044960</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4952,6 +5147,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122197113</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5064,6 +5264,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122197537</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5176,6 +5381,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122200106</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5274,6 +5484,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107044958</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5391,6 +5606,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122197684</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5497,6 +5717,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111705879</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5603,6 +5828,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111706241</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5729,8 +5959,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122198436</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>